--- a/storage/app/fleet.xlsx
+++ b/storage/app/fleet.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B72"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -975,25 +975,9 @@
         <v>XSA</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>G</v>
-      </c>
-      <c r="B73" t="str">
-        <v>AOBTB</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>D</v>
-      </c>
-      <c r="B74" t="str">
-        <v>ABBRW</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B72"/>
   </ignoredErrors>
 </worksheet>
 </file>